--- a/healthcare_forms/007_hospital_discharge_planning_feedback_evaluation_form--healthcare_forms.xlsx
+++ b/healthcare_forms/007_hospital_discharge_planning_feedback_evaluation_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_helpful'}</t>
+          <t>very_helpful</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Helpful'}</t>
+          <t>Very Helpful</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'helpful'}</t>
+          <t>helpful</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Helpful'}</t>
+          <t>Helpful</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_helpful'}</t>
+          <t>not_helpful</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Helpful'}</t>
+          <t>Not Helpful</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'very_unhelpful'}</t>
+          <t>very_unhelpful</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Very Unhelpful'}</t>
+          <t>Very Unhelpful</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'very_unhappy'}</t>
+          <t>very_unhappy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Very Unhappy'}</t>
+          <t>Very Unhappy</t>
         </is>
       </c>
     </row>
